--- a/accounts.xlsx
+++ b/accounts.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="21000" windowHeight="17175"/>
+    <workbookView windowHeight="17775"/>
   </bookViews>
   <sheets>
     <sheet name="accounts" sheetId="1" r:id="rId1"/>
@@ -27,12 +27,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>username</t>
   </si>
   <si>
     <t>password</t>
+  </si>
+  <si>
+    <t>hj6vgdc4</t>
+  </si>
+  <si>
+    <t>wsnbb12a</t>
   </si>
 </sst>
 </file>
@@ -1185,11 +1191,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="1"/>
+  <dimension ref="A1:B2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="1" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="19.25" customWidth="1"/>
-    <col min="2" max="2" width="26.5" customWidth="1"/>
+    <col min="1" max="1" width="19.2477876106195" customWidth="1"/>
+    <col min="2" max="2" width="26.5044247787611" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1200,6 +1206,14 @@
         <v>1</v>
       </c>
     </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
